--- a/docs/assets/downloads/templates/interior-design-budget.xlsx
+++ b/docs/assets/downloads/templates/interior-design-budget.xlsx
@@ -32,7 +32,7 @@
     <t>How to use</t>
   </si>
   <si>
-    <t>Choose one currency for the workbook and replace all illustrative figures with project-specific inputs. Enter additional costs as amounts, not assumed tax percentages. Blank quantities or prices leave the calculated total blank; zero is a deliberate numeric input.</t>
+    <t>Choose one currency for the workbook and replace all illustrative figures with project-specific inputs. Enter additional costs as amounts, not assumed tax percentages. Blank quantities or prices leave the calculated total blank; zero is a deliberate numeric input. After adding or removing lines, verify formula ranges and report known totals alongside all unpriced scope.</t>
   </si>
   <si>
     <t>Example status</t>
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" ht="76" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>

--- a/docs/assets/downloads/templates/interior-design-budget.xlsx
+++ b/docs/assets/downloads/templates/interior-design-budget.xlsx
@@ -9,7 +9,7 @@
     <sheet sheetId="3" name="Worked Example" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Blank Template'!$A1:$J27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Blank Template'!$1:$5</definedName>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t>Interior design budget template</t>
   </si>
@@ -57,6 +57,18 @@
   </si>
   <si>
     <t>These are educational planning aids, not legal agreements, professional certification, or instructions for construction.</t>
+  </si>
+  <si>
+    <t>Google Sheets import</t>
+  </si>
+  <si>
+    <t>Upload the XLSX to your own Drive and open it in Google Sheets. Before using it, check formulas, blank-versus-zero behavior, validation, number formats and print breaks. Keep the original XLSX. Budget calculation logic was checked in Google Sheets on September 26, 2026; review the layout of your imported copy separately.</t>
+  </si>
+  <si>
+    <t>Printing</t>
+  </si>
+  <si>
+    <t>US Letter, landscape. Fit one page wide and inspect the preview; long tables may span multiple pages.</t>
   </si>
   <si>
     <t>Step 1</t>
@@ -292,21 +304,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -320,13 +332,19 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -673,7 +691,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -728,7 +746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" ht="76" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -832,7 +850,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
@@ -848,8 +866,24 @@
         <v>41</v>
       </c>
     </row>
+    <row r="22" ht="60" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LOpenLintel | Instructions &amp;RPage &amp;P</oddFooter>
   </headerFooter>
@@ -864,11 +898,11 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="48" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -887,7 +921,7 @@
     </row>
     <row r="2" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -901,7 +935,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -915,7 +949,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -929,34 +963,34 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1321,7 +1355,7 @@
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:9" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1366,7 +1400,8 @@
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LOpenLintel | Educational planning resource &amp;RPage &amp;P</oddFooter>
   </headerFooter>
@@ -1381,11 +1416,11 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="48" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1418,7 +1453,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1432,7 +1467,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1446,48 +1481,48 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="16">
+        <v>52</v>
+      </c>
+      <c r="C6" s="17">
         <v>1</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E6" s="9">
         <v>1200</v>
@@ -1507,21 +1542,21 @@
         <v>200</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="17">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="19">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>49</v>
+      <c r="D7" s="18" t="s">
+        <v>53</v>
       </c>
       <c r="E7" s="12">
         <v>500</v>
@@ -1540,20 +1575,20 @@
         <f>IF(OR(G7="",H7=""),"",ROUND(H7-G7,2))</f>
         <v>-50</v>
       </c>
-      <c r="J7" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="16" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -1567,10 +1602,10 @@
         <v/>
       </c>
       <c r="J8" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1588,7 +1623,7 @@
       </c>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1606,7 +1641,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -1624,7 +1659,7 @@
       </c>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1642,7 +1677,7 @@
       </c>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -1660,7 +1695,7 @@
       </c>
       <c r="J13" s="10"/>
     </row>
-    <row r="14" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1678,7 +1713,7 @@
       </c>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -1696,7 +1731,7 @@
       </c>
       <c r="J15" s="10"/>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1714,7 +1749,7 @@
       </c>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -1732,7 +1767,7 @@
       </c>
       <c r="J17" s="10"/>
     </row>
-    <row r="18" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1750,7 +1785,7 @@
       </c>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -1768,7 +1803,7 @@
       </c>
       <c r="J19" s="10"/>
     </row>
-    <row r="20" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1786,7 +1821,7 @@
       </c>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1804,7 +1839,7 @@
       </c>
       <c r="J21" s="10"/>
     </row>
-    <row r="22" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1822,7 +1857,7 @@
       </c>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -1840,7 +1875,7 @@
       </c>
       <c r="J23" s="10"/>
     </row>
-    <row r="24" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1858,7 +1893,7 @@
       </c>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" ht="36" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -1878,7 +1913,7 @@
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:9" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1923,7 +1958,8 @@
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LOpenLintel | Educational planning resource &amp;RPage &amp;P</oddFooter>
   </headerFooter>
